--- a/public/flonancial_template.xlsx
+++ b/public/flonancial_template.xlsx
@@ -8,8 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WCale\Desktop\flonancial\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{134495FF-FE19-4407-BE27-58B5086FA0C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <workbookProtection lockStructure="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{854E3A82-4704-4C13-AF7E-731517DE00C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,12 +38,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="97">
   <si>
     <t>INCOME — HOW TO USE THIS TAB</t>
-  </si>
-  <si>
-    <t>Enter every payment you receive for your business or property.</t>
   </si>
   <si>
     <t>The three blue columns (Date, Description, Amount) are required. The grey columns are optional.</t>
@@ -69,12 +65,6 @@
   </si>
   <si>
     <t>IMPORTANT</t>
-  </si>
-  <si>
-    <t>Use one spreadsheet per business. If you are a sole trader, this file is for that trade.</t>
-  </si>
-  <si>
-    <t>If you are a landlord, combine all your UK properties into this one file.</t>
   </si>
   <si>
     <t>If you have BOTH a sole trade and UK property income, use a separate spreadsheet for each.</t>
@@ -140,9 +130,6 @@
     <t>EXPENSES — HOW TO USE THIS TAB</t>
   </si>
   <si>
-    <t>Enter every business expense you pay.</t>
-  </si>
-  <si>
     <t>Use DD/MM/YYYY format (e.g. 12/04/2026).</t>
   </si>
   <si>
@@ -150,39 +137,6 @@
   </si>
   <si>
     <t>The gross amount you paid (the total on the receipt or invoice).</t>
-  </si>
-  <si>
-    <t>OPTIONAL COLUMNS</t>
-  </si>
-  <si>
-    <t>Reference:</t>
-  </si>
-  <si>
-    <t>Invoice numbers, receipt locations, photo references etc.</t>
-  </si>
-  <si>
-    <t>Category:</t>
-  </si>
-  <si>
-    <t>Type of expense. A dropdown is provided, or type your own.</t>
-  </si>
-  <si>
-    <t>VAT:</t>
-  </si>
-  <si>
-    <t>If you're VAT registered, track the VAT portion here. If not (most sole traders</t>
-  </si>
-  <si>
-    <t>under £90k aren't), ignore this column. Flonancial only reads the gross Amount.</t>
-  </si>
-  <si>
-    <t>Notes:</t>
-  </si>
-  <si>
-    <t>Anything else useful.</t>
-  </si>
-  <si>
-    <t>Your paper receipts and invoices can stay on paper — this spreadsheet is your digital record.</t>
   </si>
   <si>
     <t>VAT (optional)</t>
@@ -246,9 +200,6 @@
   </si>
   <si>
     <t>Expenses</t>
-  </si>
-  <si>
-    <t>This tab is auto-calculated. Do not edit.</t>
   </si>
   <si>
     <t>Upload this file to flonancial.co.uk to submit your quarterly update.</t>
@@ -373,6 +324,12 @@
   <si>
     <t>HMRC never sees your individual transactions. The detail stays in this spreadsheet.</t>
   </si>
+  <si>
+    <t>Use one spreadsheet per business. If you are a sole trader, this file is for that trade, If you are a landlord, combine all your UK properties into this one file.</t>
+  </si>
+  <si>
+    <t>This is a protected tab, please do not edit anything on thie page.</t>
+  </si>
 </sst>
 </file>
 
@@ -439,13 +396,6 @@
     </font>
     <font>
       <b/>
-      <sz val="14"/>
-      <color rgb="FF2E88D0"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <sz val="10"/>
       <color rgb="FFCC0000"/>
       <name val="Arial"/>
@@ -472,8 +422,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -494,18 +450,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDEE9F8"/>
+        <fgColor rgb="FFE8F0FE"/>
+        <bgColor rgb="FFDEE9F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor rgb="FFE8F0FE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE8F0FE"/>
-        <bgColor rgb="FFDEE9F8"/>
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -519,6 +481,50 @@
       <top/>
       <bottom style="thin">
         <color rgb="FFD5D8DC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -542,22 +548,22 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -822,221 +828,244 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F1019"/>
+  <dimension ref="A1:G1012"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="36" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="28" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="5" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="2"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B7" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" s="6">
+        <v>46122</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="8">
+        <v>1</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="6">
+        <v>46130</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="8">
+        <v>2</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" s="6">
+        <v>46148</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="8">
         <v>3</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="D11" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" s="6">
+        <v>46162</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="8">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" s="6">
-        <v>46122</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C16" s="8">
-        <v>1</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" s="6">
-        <v>46130</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" s="8">
-        <v>2</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F17" s="7"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18" s="6">
-        <v>46148</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C18" s="8">
-        <v>3</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E18" s="7" t="s">
+      <c r="D12" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="E12" s="7" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="6">
-        <v>46162</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C19" s="8">
-        <v>4</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="F19" s="7"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" s="9"/>
+      <c r="C13" s="10"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" s="9"/>
+      <c r="C14" s="10"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" s="9"/>
+      <c r="C15" s="10"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C16" s="10"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C17" s="10"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" s="2"/>
+      <c r="C18" s="10"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" s="2"/>
+      <c r="C19" s="10"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="9"/>
       <c r="C20" s="10"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="9"/>
       <c r="C21" s="10"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="9"/>
       <c r="C22" s="10"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="9"/>
       <c r="C23" s="10"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="9"/>
       <c r="C24" s="10"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="9"/>
       <c r="C25" s="10"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="9"/>
       <c r="C26" s="10"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="9"/>
       <c r="C27" s="10"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="9"/>
       <c r="C28" s="10"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="9"/>
       <c r="C29" s="10"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="9"/>
       <c r="C30" s="10"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="9"/>
       <c r="C31" s="10"/>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="9"/>
       <c r="C32" s="10"/>
     </row>
@@ -4959,34 +4988,6 @@
     <row r="1012" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1012" s="9"/>
       <c r="C1012" s="10"/>
-    </row>
-    <row r="1013" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1013" s="9"/>
-      <c r="C1013" s="10"/>
-    </row>
-    <row r="1014" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1014" s="9"/>
-      <c r="C1014" s="10"/>
-    </row>
-    <row r="1015" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1015" s="9"/>
-      <c r="C1015" s="10"/>
-    </row>
-    <row r="1016" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1016" s="9"/>
-      <c r="C1016" s="10"/>
-    </row>
-    <row r="1017" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1017" s="9"/>
-      <c r="C1017" s="10"/>
-    </row>
-    <row r="1018" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1018" s="9"/>
-      <c r="C1018" s="10"/>
-    </row>
-    <row r="1019" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1019" s="9"/>
-      <c r="C1019" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4996,7 +4997,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G1024"/>
+  <dimension ref="A1:G1013"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -5008,265 +5009,280 @@
     <col min="7" max="7" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B7" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="5" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
+      <c r="G8" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" s="6">
+        <v>46124</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="8">
+        <v>6</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" s="8">
+        <v>9.17</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="6">
+        <v>46134</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="8">
+        <v>7</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" s="8">
+        <v>0</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" s="6">
+        <v>46143</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" s="8">
+        <v>8</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
+      <c r="G11" s="7"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" s="6">
+        <v>46156</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="8">
+        <v>9</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F12" s="8">
         <v>5</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A15" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A17" s="2" t="s">
+      <c r="G12" s="7" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A19" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F19" s="5" t="s">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" s="6">
+        <v>46170</v>
+      </c>
+      <c r="B13" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="G19" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A20" s="6">
-        <v>46124</v>
-      </c>
-      <c r="B20" s="7" t="s">
+      <c r="C13" s="8">
+        <v>121212</v>
+      </c>
+      <c r="D13" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="C20" s="8">
-        <v>6</v>
-      </c>
-      <c r="D20" s="7" t="s">
+      <c r="E13" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="F13" s="8">
+        <v>3.75</v>
+      </c>
+      <c r="G13" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="F20" s="8">
-        <v>9.17</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A21" s="6">
-        <v>46134</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C21" s="8">
-        <v>7</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="F21" s="8">
-        <v>0</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A22" s="6">
-        <v>46143</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C22" s="8">
-        <v>8</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="F22" s="8">
-        <v>2</v>
-      </c>
-      <c r="G22" s="7"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A23" s="6">
-        <v>46156</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C23" s="8">
-        <v>9</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="F23" s="8">
-        <v>5</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A24" s="6">
-        <v>46170</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C24" s="8">
-        <v>121212</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="F24" s="8">
-        <v>3.75</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" s="9"/>
+      <c r="C14" s="10"/>
+      <c r="F14" s="10"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" s="9"/>
+      <c r="C15" s="10"/>
+      <c r="F15" s="10"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" s="9"/>
+      <c r="C16" s="10"/>
+      <c r="F16" s="10"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" s="9"/>
+      <c r="C17" s="10"/>
+      <c r="F17" s="10"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18" s="9"/>
+      <c r="C18" s="10"/>
+      <c r="F18" s="10"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" s="9"/>
+      <c r="C19" s="10"/>
+      <c r="F19" s="10"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" s="9"/>
+      <c r="C20" s="10"/>
+      <c r="F20" s="10"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" s="9"/>
+      <c r="C21" s="10"/>
+      <c r="F21" s="10"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" s="9"/>
+      <c r="C22" s="10"/>
+      <c r="F22" s="10"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23" s="9"/>
+      <c r="C23" s="10"/>
+      <c r="F23" s="10"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" s="9"/>
+      <c r="C24" s="10"/>
+      <c r="F24" s="10"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="9"/>
       <c r="C25" s="10"/>
       <c r="F25" s="10"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="9"/>
       <c r="C26" s="10"/>
       <c r="F26" s="10"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="9"/>
       <c r="C27" s="10"/>
       <c r="F27" s="10"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="9"/>
       <c r="C28" s="10"/>
       <c r="F28" s="10"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="9"/>
       <c r="C29" s="10"/>
       <c r="F29" s="10"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="9"/>
       <c r="C30" s="10"/>
       <c r="F30" s="10"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="9"/>
       <c r="C31" s="10"/>
       <c r="F31" s="10"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="9"/>
       <c r="C32" s="10"/>
       <c r="F32" s="10"/>
@@ -10176,64 +10192,9 @@
       <c r="C1013" s="10"/>
       <c r="F1013" s="10"/>
     </row>
-    <row r="1014" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1014" s="9"/>
-      <c r="C1014" s="10"/>
-      <c r="F1014" s="10"/>
-    </row>
-    <row r="1015" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1015" s="9"/>
-      <c r="C1015" s="10"/>
-      <c r="F1015" s="10"/>
-    </row>
-    <row r="1016" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1016" s="9"/>
-      <c r="C1016" s="10"/>
-      <c r="F1016" s="10"/>
-    </row>
-    <row r="1017" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1017" s="9"/>
-      <c r="C1017" s="10"/>
-      <c r="F1017" s="10"/>
-    </row>
-    <row r="1018" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1018" s="9"/>
-      <c r="C1018" s="10"/>
-      <c r="F1018" s="10"/>
-    </row>
-    <row r="1019" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1019" s="9"/>
-      <c r="C1019" s="10"/>
-      <c r="F1019" s="10"/>
-    </row>
-    <row r="1020" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1020" s="9"/>
-      <c r="C1020" s="10"/>
-      <c r="F1020" s="10"/>
-    </row>
-    <row r="1021" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1021" s="9"/>
-      <c r="C1021" s="10"/>
-      <c r="F1021" s="10"/>
-    </row>
-    <row r="1022" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1022" s="9"/>
-      <c r="C1022" s="10"/>
-      <c r="F1022" s="10"/>
-    </row>
-    <row r="1023" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1023" s="9"/>
-      <c r="C1023" s="10"/>
-      <c r="F1023" s="10"/>
-    </row>
-    <row r="1024" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1024" s="9"/>
-      <c r="C1024" s="10"/>
-      <c r="F1024" s="10"/>
-    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" promptTitle="Category" prompt="Optional: pick a category" sqref="E20:E1024" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" promptTitle="Category" prompt="Optional: pick a category" sqref="E9:E1013" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Travel,Software,Office,Phone,Insurance,Professional fees,Marketing,Equipment,Other"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -10252,211 +10213,211 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="B1" s="12">
+      <c r="A1" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="16">
         <f>SUM(Income!C:C)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="18" x14ac:dyDescent="0.35">
-      <c r="A2" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="B2" s="14">
+    <row r="2" spans="1:2" ht="18.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" s="18">
         <f>SUM(Expenses!C:C)</f>
         <v>121242</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="15" t="s">
-        <v>69</v>
+      <c r="A4" s="11" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="s">
-        <v>70</v>
+      <c r="A5" s="12" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="B19" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="C19" s="17" t="s">
-        <v>80</v>
+      <c r="A19" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" s="18" t="s">
-        <v>93</v>
+      <c r="A25" s="14" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/public/flonancial_template.xlsx
+++ b/public/flonancial_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WCale\Desktop\flonancial\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{854E3A82-4704-4C13-AF7E-731517DE00C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C4A4437-37A2-40DF-B5AB-F85D9462BA33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="99">
   <si>
     <t>INCOME — HOW TO USE THIS TAB</t>
   </si>
@@ -328,7 +328,13 @@
     <t>Use one spreadsheet per business. If you are a sole trader, this file is for that trade, If you are a landlord, combine all your UK properties into this one file.</t>
   </si>
   <si>
-    <t>This is a protected tab, please do not edit anything on thie page.</t>
+    <t>These totals are calculated automatically, please do not edit anything on thie page.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Please use this as your primary record, not a copy of another document. </t>
+  </si>
+  <si>
+    <t>HMRC requires records to be kept digitally from the start.</t>
   </si>
 </sst>
 </file>
@@ -404,13 +410,6 @@
     <font>
       <b/>
       <sz val="10"/>
-      <color rgb="FF2E88D0"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
       <color rgb="FF0F1C2E"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -425,6 +424,12 @@
     <font>
       <b/>
       <sz val="14"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -549,20 +554,22 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -835,7 +842,8 @@
     <col min="2" max="2" width="36" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="28" customWidth="1"/>
-    <col min="5" max="6" width="14" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="14" style="8" customWidth="1"/>
     <col min="7" max="7" width="30" customWidth="1"/>
   </cols>
   <sheetData>
@@ -843,6 +851,7 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="F1"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
@@ -866,6 +875,7 @@
       <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
+      <c r="F4"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
@@ -874,6 +884,7 @@
       <c r="B5" s="2" t="s">
         <v>7</v>
       </c>
+      <c r="F5"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
@@ -882,11 +893,13 @@
       <c r="B6" s="2" t="s">
         <v>95</v>
       </c>
+      <c r="F6"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B7" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="F7"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
@@ -919,7 +932,7 @@
         <v>16</v>
       </c>
       <c r="C9" s="8">
-        <v>1</v>
+        <v>140</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>17</v>
@@ -927,7 +940,9 @@
       <c r="E9" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F9" s="7"/>
+      <c r="F9" s="8">
+        <v>0</v>
+      </c>
       <c r="G9" s="7" t="s">
         <v>19</v>
       </c>
@@ -940,7 +955,7 @@
         <v>20</v>
       </c>
       <c r="C10" s="8">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>21</v>
@@ -948,7 +963,9 @@
       <c r="E10" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F10" s="7"/>
+      <c r="F10" s="8">
+        <v>0</v>
+      </c>
       <c r="G10" s="7"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
@@ -959,7 +976,7 @@
         <v>22</v>
       </c>
       <c r="C11" s="8">
-        <v>3</v>
+        <v>120</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>23</v>
@@ -967,7 +984,9 @@
       <c r="E11" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="F11" s="7"/>
+      <c r="F11" s="8">
+        <v>0</v>
+      </c>
       <c r="G11" s="7" t="s">
         <v>25</v>
       </c>
@@ -980,7 +999,7 @@
         <v>26</v>
       </c>
       <c r="C12" s="8">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>27</v>
@@ -988,7 +1007,9 @@
       <c r="E12" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="F12" s="7"/>
+      <c r="F12" s="8">
+        <v>0</v>
+      </c>
       <c r="G12" s="7"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
@@ -5087,7 +5108,7 @@
         <v>34</v>
       </c>
       <c r="C9" s="8">
-        <v>6</v>
+        <v>45.85</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>35</v>
@@ -5110,7 +5131,7 @@
         <v>38</v>
       </c>
       <c r="C10" s="8">
-        <v>7</v>
+        <v>78.8</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>39</v>
@@ -5133,7 +5154,7 @@
         <v>42</v>
       </c>
       <c r="C11" s="8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>43</v>
@@ -5154,7 +5175,7 @@
         <v>44</v>
       </c>
       <c r="C12" s="8">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>45</v>
@@ -5177,7 +5198,7 @@
         <v>48</v>
       </c>
       <c r="C13" s="8">
-        <v>121212</v>
+        <v>22.5</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>49</v>
@@ -10206,28 +10227,28 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="3" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="16">
+      <c r="B1" s="15">
         <f>SUM(Income!C:C)</f>
-        <v>10</v>
+        <v>400</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="18.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="B2" s="18">
+      <c r="B2" s="17">
         <f>SUM(Expenses!C:C)</f>
-        <v>121242</v>
+        <v>182.15</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -10235,188 +10256,198 @@
         <v>96</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="12" t="s">
-        <v>54</v>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="18" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="18" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
         <v>55</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" s="3" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" s="2" t="s">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17" s="1" t="s">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19" s="13" t="s">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="B19" s="13" t="s">
+      <c r="B21" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="C21" s="12" t="s">
         <v>64</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B25" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C25" s="2" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" s="14" t="s">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" s="13" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27" s="1" t="s">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A29" s="3" t="s">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" s="3" t="s">
         <v>79</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A30" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A31" s="2" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A33" s="2" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A36" s="2" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A37" s="1" t="s">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A39" s="1" t="s">
         <v>84</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A39" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A40" s="3" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A42" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A43" s="2" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A42" s="2" t="s">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A44" s="2" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A45" s="1" t="s">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A47" s="1" t="s">
         <v>89</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A47" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A48" s="2" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A51" s="2" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A54" s="2" t="s">
         <v>94</v>
       </c>
     </row>
